--- a/Employee_Reports_wi52/Dennis Delfino Daginotan Q0471.xlsx
+++ b/Employee_Reports_wi52/Dennis Delfino Daginotan Q0471.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-118</v>
+        <v>-126</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-127</v>
+        <v>-135</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -995,11 +995,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
